--- a/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clémence rentre du jardin. Maman est près du lavabo. Clémence va aux toilettes. Après les toilettes, maman dit : on lave. Clémence ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Clémence va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Maman dit : savon et eau. Après les toilettes. Avant de manger aussi. Clémence sourit. Ses mains sentent le savon.</t>
+          <t>Clémence rentre du jardin. Maman est près du lavabo. Clémence va aux toilettes. Après les toilettes, On lave. Clémence ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Clémence va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Clémence sourit. Ses mains sentent le savon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clémence rentre du jardin. Maman est près du lavabo. Clémence va aux toilettes. Après les toilettes,
+maman|On lave.
+narrateur|Clémence ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Clémence va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie.
+maman|Savon et eau. Après les toilettes. Avant de manger aussi.
+narrateur|Clémence sourit. Ses mains sentent le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Clémence se lave les mains. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Après les toilettes, Clémence a lavé. Avant de manger, Clémence a lavé. Savon et eau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Clémence s'assoit près de maman. Ses mains sont propres.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Clémence sourit. Ses mains sentent le savon.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Clémence se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Après les toilettes, Clémence a lavé. Avant de manger, Clémence a lavé. Savon et eau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Clémence s'assoit près de maman. Ses mains sont propres.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clémence lave ses mains</t>
+          <t>Le carré de soleil de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le volet tape. Sarah rentre du jardin, se lave au savon citron après les toilettes, puis encore avant de manger. Le carré de soleil reste sur le sol.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Clémence rentre du jardin. Maman est près du lavabo. Clémence va aux toilettes. Après les toilettes, On lave. Clémence ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Clémence va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Clémence sourit. Ses mains sentent le savon.</t>
+          <t>Le volet de bois tape doucement. Un carré de soleil est au sol. Ça sent la soupe. Les chaussures du jardin sont là. Elles sont un peu mouillées. Un oiseau chante dehors. Le vent pousse le volet. Sarah, rentre. Le lavabo t'attend. J'arrive, maman. Tu vois le carré de soleil ? Oui. Il est chaud. En ce moment, Sarah rentre. Elle rentre du jardin. Elle laisse les chaussures. Elle va aux toilettes. Après les toilettes, on lave. Je viens. Sarah ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Ça sent le citron. Oui. Frotte tes mains. Sarah frotte ses mains. Elle frotte le dessus. Elle frotte le dessous. Elle rince. Les bulles partent. Elle essuie. Les mains sont propres. Bravo, Sarah. Tu as fait du bon travail. Mes mains sentent le citron. Oui. C'est le savon. Le carré de soleil bouge un peu. C'est l'heure de manger. Avant de manger, on lave. Je vais au lavabo. Sarah ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Savon et eau. Tu as fini tes mains ? Oui, maman. Bravo. Sarah sourit. Ses mains sentent le savon. Le volet tape encore un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Clémence rentre du jardin. Maman est près du lavabo. Clémence va aux toilettes. Après les toilettes,
-maman|On lave.
-narrateur|Clémence ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Clémence va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie.
-maman|Savon et eau. Après les toilettes. Avant de manger aussi.
-narrateur|Clémence sourit. Ses mains sentent le savon.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le volet de bois tape doucement.
+narrateur|Un carré de soleil est au sol.
+narrateur|Ça sent la soupe.
+narrateur|Les chaussures du jardin sont là.
+narrateur|Elles sont un peu mouillées.
+narrateur|Un oiseau chante dehors.
+narrateur|Le vent pousse le volet.
+maman|Sarah, rentre. Le lavabo t'attend.
+enfant-f|J'arrive, maman.
+maman|Tu vois le carré de soleil ?
+enfant-f|Oui. Il est chaud.
+narrateur|En ce moment, Sarah rentre.
+narrateur|Elle rentre du jardin.
+narrateur|Elle laisse les chaussures.
+narrateur|Elle va aux toilettes.
+maman|Après les toilettes, on lave.
+enfant-f|Je viens.
+narrateur|Sarah ouvre l'eau.
+narrateur|L'eau est tiède.
+narrateur|Elle prend le savon.
+narrateur|Le savon sent le citron.
+enfant-f|Ça sent le citron.
+maman|Oui. Frotte tes mains.
+narrateur|Sarah frotte ses mains.
+narrateur|Elle frotte le dessus.
+narrateur|Elle frotte le dessous.
+narrateur|Elle rince.
+narrateur|Les bulles partent.
+narrateur|Elle essuie.
+narrateur|Les mains sont propres.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+enfant-f|Mes mains sentent le citron.
+maman|Oui. C'est le savon.
+narrateur|Le carré de soleil bouge un peu.
+maman|C'est l'heure de manger.
+maman|Avant de manger, on lave.
+enfant-f|Je vais au lavabo.
+narrateur|Sarah ouvre l'eau.
+narrateur|Elle prend le savon.
+narrateur|Elle frotte.
+narrateur|Elle rince.
+narrateur|Elle essuie.
+maman|Savon et eau.
+maman|Après les toilettes.
+maman|Avant de manger aussi.
+enfant-f|Savon et eau.
+maman|Tu as fini tes mains ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|Sarah sourit.
+narrateur|Ses mains sentent le savon.
+narrateur|Le volet tape encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Clémence se lave les mains. Avec quoi ?</t>
+          <t>Sarah se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1563,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Clémence se lave les mains. Avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah se lave les mains.
+narrateur|Avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Après les toilettes, Clémence a lavé. Avant de manger, Clémence a lavé. Savon et eau.</t>
+          <t>Après les toilettes, Sarah a lavé. Avant de manger, Sarah a lavé. Savon et eau. Tu te souviens du savon citron ? Oui. Savon et eau. Bravo, Sarah. Le volet tape encore un peu. Le carré de soleil reste au sol. Les chaussures sèchent près de la porte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1735,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Après les toilettes, Clémence a lavé. Avant de manger, Clémence a lavé. Savon et eau.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Après les toilettes, Sarah a lavé.
+narrateur|Avant de manger, Sarah a lavé.
+narrateur|Savon et eau.
+maman|Tu te souviens du savon citron ?
+enfant-f|Oui. Savon et eau.
+maman|Bravo, Sarah.
+narrateur|Le volet tape encore un peu.
+narrateur|Le carré de soleil reste au sol.
+narrateur|Les chaussures sèchent près de la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Clémence s'assoit près de maman. Ses mains sont propres.</t>
+          <t>Sarah s'assoit près de maman. Ses mains sont propres. Tu as les mains propres ? Oui, maman. Bravo. On mange. La soupe est chaude. Le carré de soleil touche la table. Mes mains sentent le citron. Oui. C'est le savon. L'oiseau chante encore dehors.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1910,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Clémence s'assoit près de maman. Ses mains sont propres.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah s'assoit près de maman.
+narrateur|Ses mains sont propres.
+maman|Tu as les mains propres ?
+enfant-f|Oui, maman.
+maman|Bravo. On mange.
+narrateur|La soupe est chaude.
+narrateur|Le carré de soleil touche la table.
+enfant-f|Mes mains sentent le citron.
+maman|Oui. C'est le savon.
+narrateur|L'oiseau chante encore dehors.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1946,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah a lavé après les toilettes. Sarah a lavé avant de manger. Bravo, Sarah. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2086,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah a lavé après les toilettes.
+narrateur|Sarah a lavé avant de manger.
+maman|Bravo, Sarah.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le volet de bois tape doucement. Un carré de soleil est au sol. Ça sent la soupe. Les chaussures du jardin sont là. Elles sont un peu mouillées. Un oiseau chante dehors. Le vent pousse le volet. Sarah, rentre. Le lavabo t'attend. J'arrive, maman. Tu vois le carré de soleil ? Oui. Il est chaud. En ce moment, Sarah rentre. Elle rentre du jardin. Elle laisse les chaussures. Elle va aux toilettes. Après les toilettes, on lave. Je viens. Sarah ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Ça sent le citron. Oui. Frotte tes mains. Sarah frotte ses mains. Elle frotte le dessus. Elle frotte le dessous. Elle rince. Les bulles partent. Elle essuie. Les mains sont propres. Bravo, Sarah. Tu as fait du bon travail. Mes mains sentent le citron. Oui. C'est le savon. Le carré de soleil bouge un peu. C'est l'heure de manger. Avant de manger, on lave. Je vais au lavabo. Sarah ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Savon et eau. Tu as fini tes mains ? Oui, maman. Bravo. Sarah sourit. Ses mains sentent le savon. Le volet tape encore un peu.</t>
+          <t>Le volet de bois tape doucement. Un carré de soleil est au sol. Ça sent la soupe. Les chaussures du jardin sont là. Elles sont un peu mouillées. Un oiseau chante dehors. Le vent pousse le volet. Sarah, rentre. Le lavabo t'attend. J'arrive, maman. Tu vois le carré de soleil ? Oui. Il est chaud. En ce moment, Sarah rentre. Elle rentre du jardin. Elle pose un pied sur le carré. Le carré est chaud. Elle laisse les chaussures. Elle va aux toilettes. Après les toilettes, on lave. Je viens. Sarah ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Ça sent le citron. Oui. Frotte tes mains. Sarah frotte ses mains. Elle frotte le dessus. Elle frotte le dessous. Elle rince. Les bulles partent. Elle essuie. Les mains sont propres. Bravo, Sarah. Mes mains sentent le citron. Oui. C'est le savon. Le carré de soleil bouge un peu. C'est l'heure de manger. Avant de manger, on lave. Je vais au lavabo. Sarah ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Savon et eau. Tu as fini tes mains ? Oui, maman. Bravo. Sarah regarde ses mains. Ses mains sentent le savon. Le volet tape encore un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clémence rentre du jardin. Maman est près du lavabo. Clémence va aux toilettes. Après les toilettes, maman dit : on lave. Clémence ouvre l'eau. L'eau est tiède. Elle prend le &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;. Le savon sent le citron. Elle frotte ses mains. Elle rince. Elle essuie. Les mains sont propres. C'est l'heure de manger. Avant de manger, Clémence va au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Maman dit : savon et eau. Après les toilettes. Avant de manger aussi. Clémence sourit. Ses mains sentent le savon.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le volet de bois tape doucement. Un carré de soleil est au sol. Ça sent la soupe. Les chaussures du jardin sont là. Elles sont un peu mouillées. Un oiseau chante dehors. Le vent pousse le volet. Sarah, rentre. Le lavabo t'attend. J'arrive, maman. Tu vois le carré de soleil ? Oui. Il est chaud. En ce moment, Sarah rentre. Elle rentre du jardin. Elle pose un pied sur le carré. Le carré est chaud. Elle laisse les chaussures. Elle va aux toilettes. Après les toilettes, on lave. Je viens. Sarah ouvre l'eau. L'eau est tiède. Elle prend le savon. Le savon sent le citron. Ça sent le citron. Oui. Frotte tes mains. Sarah frotte ses mains. Elle frotte le dessus. Elle frotte le dessous. Elle rince. Les bulles partent. Elle essuie. Les mains sont propres. Bravo, Sarah. Mes mains sentent le citron. Oui. C'est le savon. Le carré de soleil bouge un peu. C'est l'heure de manger. Avant de manger, on lave. Je vais au lavabo. Sarah ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Elle essuie. Savon et eau. Après les toilettes. Avant de manger aussi. Savon et eau. Tu as fini tes mains ? Oui, maman. Bravo. Sarah regarde ses mains. Ses mains sentent le savon. Le volet tape encore un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1337,6 +1337,8 @@
 enfant-f|Oui. Il est chaud.
 narrateur|En ce moment, Sarah rentre.
 narrateur|Elle rentre du jardin.
+narrateur|Elle pose un pied sur le carré.
+narrateur|Le carré est chaud.
 narrateur|Elle laisse les chaussures.
 narrateur|Elle va aux toilettes.
 maman|Après les toilettes, on lave.
@@ -1355,7 +1357,6 @@
 narrateur|Elle essuie.
 narrateur|Les mains sont propres.
 maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
 enfant-f|Mes mains sentent le citron.
 maman|Oui. C'est le savon.
 narrateur|Le carré de soleil bouge un peu.
@@ -1374,7 +1375,7 @@
 maman|Tu as fini tes mains ?
 enfant-f|Oui, maman.
 maman|Bravo.
-narrateur|Sarah sourit.
+narrateur|Sarah regarde ses mains.
 narrateur|Ses mains sentent le savon.
 narrateur|Le volet tape encore un peu.</t>
         </is>
@@ -1408,7 +1409,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clémence se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1596,7 +1597,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après les toilettes, Clémence a lavé. Avant de manger, Clémence a lavé. &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt; et eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après les toilettes, Sarah a lavé. Avant de manger, Sarah a lavé. Savon et eau. Tu te souviens du savon citron ? Oui. Savon et eau. Bravo, Sarah. Le volet tape encore un peu. Le carré de soleil reste au sol. Les chaussures sèchent près de la porte.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1775,7 +1776,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Clémence s'assoit près de maman. Ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s sont propres.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah s'assoit près de maman. Ses mains sont propres. Tu as les mains propres ? Oui, maman. Bravo. On mange. La soupe est chaude. Le carré de soleil touche la table. Mes mains sentent le citron. Oui. C'est le savon. L'oiseau chante encore dehors.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1946,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sarah a lavé après les toilettes. Sarah a lavé avant de manger. Bravo, Sarah. L'histoire est finie.</t>
+          <t>Sarah a lavé après les toilettes. Sarah a lavé avant de manger. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a lavé après les toilettes. Sarah a lavé avant de manger. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2088,8 +2089,7 @@
         <is>
           <t>narrateur|Sarah a lavé après les toilettes.
 narrateur|Sarah a lavé avant de manger.
-maman|Bravo, Sarah.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Sarah.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2155,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison, lavabo</t>
+          <t>jardin puis maison, lavabo</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Clémence, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
